--- a/Data/raw_data/human_rights_risk_&_responsiveness.xlsx
+++ b/Data/raw_data/human_rights_risk_&_responsiveness.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536F1C0C-3070-0141-BDF1-11F4B4C404EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13262CBF-2CC0-FD4B-8480-5739A059C690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="1820" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -165,6 +165,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -186,11 +193,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,16 +469,16 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>10</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>25</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>96</v>
       </c>
     </row>
@@ -478,16 +486,16 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>3</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>10</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>25</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>96</v>
       </c>
     </row>
@@ -495,16 +503,16 @@
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4">
         <v>50</v>
       </c>
     </row>
@@ -512,16 +520,16 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
         <v>6</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>7</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>72</v>
       </c>
     </row>
@@ -529,16 +537,16 @@
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
         <v>3</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>67</v>
       </c>
     </row>
@@ -546,16 +554,16 @@
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
         <v>27</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>20</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>85</v>
       </c>
     </row>
@@ -563,16 +571,16 @@
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
         <v>17</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>6</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>50</v>
       </c>
     </row>
@@ -580,118 +588,118 @@
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3">
-        <v>100</v>
+      <c r="B9" s="4">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4">
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4">
         <v>5</v>
       </c>
-      <c r="E10" s="3">
-        <v>80</v>
+      <c r="E10" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3">
-        <v>15</v>
-      </c>
-      <c r="E12" s="3">
-        <v>80</v>
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
         <v>10</v>
       </c>
-      <c r="D13" s="3">
-        <v>4</v>
-      </c>
-      <c r="E13" s="3">
-        <v>25</v>
+      <c r="D13" s="4">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="C14" s="3">
-        <v>10</v>
-      </c>
-      <c r="D14" s="3">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>50</v>
+      <c r="E14" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="B15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="3">
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
         <v>100</v>
       </c>
     </row>
@@ -699,101 +707,101 @@
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>100</v>
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5</v>
+      </c>
+      <c r="E16" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>40</v>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3</v>
+      </c>
+      <c r="D17" s="4">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="C18" s="3">
-        <v>3</v>
-      </c>
-      <c r="D18" s="3">
-        <v>6</v>
-      </c>
-      <c r="E18" s="3">
-        <v>34</v>
+      <c r="E18" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>5</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3">
-        <v>7</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4">
         <v>100</v>
       </c>
     </row>
@@ -801,16 +809,16 @@
       <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="3">
-        <v>0</v>
-      </c>
-      <c r="C22" s="3">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
         <v>100</v>
       </c>
     </row>
@@ -818,33 +826,33 @@
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3">
-        <v>0</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2</v>
-      </c>
-      <c r="D23" s="3">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3">
-        <v>100</v>
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
+        <v>5</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-      <c r="C24" s="3">
-        <v>2</v>
-      </c>
-      <c r="D24" s="3">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4">
         <v>0</v>
       </c>
     </row>
@@ -852,33 +860,33 @@
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="3">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="B26" s="4">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
         <v>100</v>
       </c>
     </row>
@@ -886,50 +894,50 @@
       <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3">
-        <v>0</v>
-      </c>
-      <c r="C27" s="3">
-        <v>6</v>
-      </c>
-      <c r="D27" s="3">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>5</v>
+      </c>
+      <c r="E27" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>0</v>
-      </c>
-      <c r="C28" s="3">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3">
-        <v>5</v>
-      </c>
-      <c r="E28" s="3">
-        <v>60</v>
+      <c r="B28" s="4">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
+      <c r="B29" s="4">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
         <v>0</v>
       </c>
     </row>
@@ -937,16 +945,16 @@
       <c r="A30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="3">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3">
-        <v>2</v>
-      </c>
-      <c r="D30" s="3">
-        <v>2</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="B30" s="4">
+        <v>0</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="E30" s="4">
         <v>0</v>
       </c>
     </row>
@@ -954,33 +962,33 @@
       <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3">
-        <v>2</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
+      <c r="B31" s="4">
+        <v>0</v>
+      </c>
+      <c r="C31" s="4">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="3">
-        <v>0</v>
-      </c>
-      <c r="C32" s="3">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="B32" s="4">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
         <v>0</v>
       </c>
     </row>
@@ -992,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" s="3">
         <v>0</v>
